--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-07-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -617,7 +617,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£10.55</t>
+          <t>£10.52</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationsuperstore.co.uk/product/celotex-30mm-tb4030-insulation-board-2400mm-x-1200mm.html</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -738,7 +738,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£12.35</t>
+          <t>£12.29</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>£16.50</t>
+          <t>Error: 504 Server Error: Gateway Time-out for url: https://www.insulationsuperstore.co.uk/product/celotex-40mm-tb4040-insulation-board-2400mm-x-1200mm.html</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -859,7 +859,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>£15.0</t>
+          <t>£14.93</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -980,7 +980,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>£18.42</t>
+          <t>£17.14</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>£22.52</t>
+          <t>£20.47</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>Error: 504 Server Error: Gateway Time-out for url: https://www.insulationsuperstore.co.uk/product/celotex-70mm-ga4070-insulation-board-2-4m-x-1-2m-17.html</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>£22.49</t>
+          <t>£22.34</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationsuperstore.co.uk/product/celotex-75mm-ga4075-insulation-board-2400mm-x-1200mm.html</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>£22.68</t>
+          <t>£22.52</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>Error: 504 Server Error: Gateway Time-out for url: https://www.insulationsuperstore.co.uk/product/celotex-80mm-ga4080-insulation-board-2400mm-x-1200mm.html</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>£26.82</t>
+          <t>£24.64</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>Error: 504 Server Error: Gateway Time-out for url: https://www.insulationsuperstore.co.uk/product/celotex-90mm-ga4090-insulation-board-2400mm-x-1200mm.html</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>£27.69</t>
+          <t>£27.5</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£28.81</t>
+          <t>£28.71</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>£36.02</t>
+          <t>£32.97</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>£41.59</t>
+          <t>£38.6</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>£45.54</t>
+          <t>£43.83</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£45.85</t>
+          <t>£42.21</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>£768.52</t>
+          <t>£653.19</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72b33e935+77845]
-	GetHandleVerifier [0x0x7ff72b33e990+77936]
-	(No symbol) [0x0x7ff72b0f9cda]
-	(No symbol) [0x0x7ff72b1506aa]
-	(No symbol) [0x0x7ff72b15095c]
-	(No symbol) [0x0x7ff72b1a3d07]
-	(No symbol) [0x0x7ff72b17890f]
-	(No symbol) [0x0x7ff72b1a0b07]
-	(No symbol) [0x0x7ff72b1786a3]
-	(No symbol) [0x0x7ff72b141791]
-	(No symbol) [0x0x7ff72b142523]
-	GetHandleVerifier [0x0x7ff72b61684d+3059501]
-	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
-	GetHandleVerifier [0x0x7ff72b630400+3164896]
-	GetHandleVerifier [0x0x7ff72b358c3e+185118]
-	GetHandleVerifier [0x0x7ff72b36054f+216111]
-	GetHandleVerifier [0x0x7ff72b3472e4+113092]
-	GetHandleVerifier [0x0x7ff72b347499+113529]
-	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	GetHandleVerifier [0x0x7ff683f0e935+77845]
+	GetHandleVerifier [0x0x7ff683f0e990+77936]
+	(No symbol) [0x0x7ff683cc9cda]
+	(No symbol) [0x0x7ff683d206aa]
+	(No symbol) [0x0x7ff683d2095c]
+	(No symbol) [0x0x7ff683d73d07]
+	(No symbol) [0x0x7ff683d4890f]
+	(No symbol) [0x0x7ff683d70b07]
+	(No symbol) [0x0x7ff683d486a3]
+	(No symbol) [0x0x7ff683d11791]
+	(No symbol) [0x0x7ff683d12523]
+	GetHandleVerifier [0x0x7ff6841e684d+3059501]
+	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff684200400+3164896]
+	GetHandleVerifier [0x0x7ff683f28c3e+185118]
+	GetHandleVerifier [0x0x7ff683f3054f+216111]
+	GetHandleVerifier [0x0x7ff683f172e4+113092]
+	GetHandleVerifier [0x0x7ff683f17499+113529]
+	GetHandleVerifier [0x0x7ff683efe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
